--- a/Jogos_do_Dia/FootyStats/ligas_footystats.xlsx
+++ b/Jogos_do_Dia/FootyStats/ligas_footystats.xlsx
@@ -373,7 +373,7 @@
     <t>[{'id': 100, 'year': 2017, 'country': 'Brazil'}, {'id': 101, 'year': 2016, 'country': 'Brazil'}, {'id': 580, 'year': 2015, 'country': 'Brazil'}, {'id': 581, 'year': 2014, 'country': 'Brazil'}, {'id': 582, 'year': 2013, 'country': 'Brazil'}, {'id': 1198, 'year': 2018, 'country': 'Brazil'}, {'id': 1936, 'year': 2019, 'country': 'Brazil'}, {'id': 3817, 'year': 2020, 'country': 'Brazil'}, {'id': 5713, 'year': 2021, 'country': 'Brazil'}, {'id': 7097, 'year': 2022, 'country': 'Brazil'}, {'id': 9035, 'year': 2023, 'country': 'Brazil'}, {'id': 11321, 'year': 2024, 'country': 'Brazil'}, {'id': 14231, 'year': 2025, 'country': 'Brazil'}]</t>
   </si>
   <si>
-    <t>[{'id': 102, 'year': 2014, 'country': 'Brazil'}, {'id': 103, 'year': 2013, 'country': 'Brazil'}, {'id': 113, 'year': 2015, 'country': 'Brazil'}, {'id': 193, 'year': 2017, 'country': 'Brazil'}, {'id': 1199, 'year': 2018, 'country': 'Brazil'}, {'id': 1937, 'year': 2019, 'country': 'Brazil'}, {'id': 4565, 'year': 2020, 'country': 'Brazil'}, {'id': 5721, 'year': 2021, 'country': 'Brazil'}, {'id': 5855, 'year': 2016, 'country': 'Brazil'}, {'id': 7107, 'year': 2022, 'country': 'Brazil'}, {'id': 9042, 'year': 2023, 'country': 'Brazil'}, {'id': 11351, 'year': 2024, 'country': 'Brazil'}]</t>
+    <t>[{'id': 102, 'year': 2014, 'country': 'Brazil'}, {'id': 103, 'year': 2013, 'country': 'Brazil'}, {'id': 113, 'year': 2015, 'country': 'Brazil'}, {'id': 193, 'year': 2017, 'country': 'Brazil'}, {'id': 1199, 'year': 2018, 'country': 'Brazil'}, {'id': 1937, 'year': 2019, 'country': 'Brazil'}, {'id': 4565, 'year': 2020, 'country': 'Brazil'}, {'id': 5721, 'year': 2021, 'country': 'Brazil'}, {'id': 5855, 'year': 2016, 'country': 'Brazil'}, {'id': 7107, 'year': 2022, 'country': 'Brazil'}, {'id': 9042, 'year': 2023, 'country': 'Brazil'}, {'id': 11351, 'year': 2024, 'country': 'Brazil'}, {'id': 14305, 'year': 2025, 'country': 'Brazil'}]</t>
   </si>
   <si>
     <t>[{'id': 690, 'year': 20172018, 'country': 'Bulgaria'}, {'id': 691, 'year': 20162017, 'country': 'Bulgaria'}, {'id': 692, 'year': 20152016, 'country': 'Bulgaria'}, {'id': 694, 'year': 20142015, 'country': 'Bulgaria'}, {'id': 695, 'year': 20132014, 'country': 'Bulgaria'}, {'id': 1547, 'year': 20182019, 'country': 'Bulgaria'}, {'id': 2285, 'year': 20192020, 'country': 'Bulgaria'}, {'id': 4574, 'year': 20202021, 'country': 'Bulgaria'}, {'id': 6012, 'year': 20212022, 'country': 'Bulgaria'}, {'id': 7483, 'year': 20222023, 'country': 'Bulgaria'}, {'id': 9551, 'year': 20232024, 'country': 'Bulgaria'}, {'id': 13863, 'year': 20242025, 'country': 'Bulgaria'}]</t>
